--- a/Q4/表1_Q4-2.xlsx
+++ b/Q4/表1_Q4-2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="表1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>72022.399</v>
+        <v>72020.5433</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>44476.6136</v>
+        <v>44475.1059</v>
       </c>
     </row>
     <row r="7">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>53708.5934</v>
+        <v>53699.5581</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>24814.379</v>
+        <v>24809.2081</v>
       </c>
     </row>
     <row r="13">
